--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -1491,7 +1491,7 @@
     <t>bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {bodySite}
+    <t xml:space="preserve">Extension {bodySite|5.2.0}
 </t>
   </si>
   <si>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase|1.3.0-dev</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -458,7 +458,7 @@
     <t>requestDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>requestAuthoredOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -498,7 +498,7 @@
     <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -515,7 +515,7 @@
     <t>requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -532,7 +532,7 @@
     <t>uncategorizedComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_UncategorizedComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_UncategorizedComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -718,7 +718,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -812,7 +812,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -909,7 +909,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
 </t>
   </si>
   <si>
@@ -971,7 +971,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -995,7 +995,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1004,7 +1004,7 @@
     <t>MedicationAdministration.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev)
 </t>
   </si>
   <si>
@@ -1037,7 +1037,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Group)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
 </t>
   </si>
   <si>
@@ -1062,7 +1062,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
+    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1197,7 +1197,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1209,7 +1209,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1252,7 +1252,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest)
+    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device)
+    <t xml:space="preserve">Reference(Device|4.0.1)
 </t>
   </si>
   <si>
@@ -1368,7 +1368,7 @@
     <t>dosageComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1384,7 +1384,7 @@
     <t>device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1400,7 +1400,7 @@
     <t>line</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1416,7 +1416,7 @@
     <t>lineComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1432,7 +1432,7 @@
     <t>rateComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1470,7 +1470,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用する。要約コード、または場所の非常に正確な定義への参照、あるいはその両方である可能性がある。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1507,7 +1507,7 @@
     <t>siteComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1578,7 +1578,7 @@
     <t>患者への、または患者への治療薬の投与経路または生理学的経路を指定するコード。たとえば、局所、静脈内など。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1599,7 +1599,7 @@
     <t>routeComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1630,7 +1630,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1651,7 +1651,7 @@
     <t>methodComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1682,7 +1682,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit1.id</t>
@@ -1842,7 +1842,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.id</t>
@@ -1887,7 +1887,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity}</t>
+Quantity {SimpleQuantity|4.0.1}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1942,7 +1942,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
 </t>
   </si>
   <si>
@@ -1961,7 +1961,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1971,7 +1971,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -2301,7 +2301,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="103.5078125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2316,7 +2316,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="64.84375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration-injection.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-medicationadministration-injection.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase|1.3.0-dev</t>
+    <t>http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationAdministrationBase</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -367,7 +367,7 @@
     <t>人間の言語。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -458,7 +458,7 @@
     <t>requestDepartment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestDepartment}
 </t>
   </si>
   <si>
@@ -482,7 +482,7 @@
     <t>requestAuthoredOn</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_RequestAuthoredOn}
 </t>
   </si>
   <si>
@@ -498,7 +498,7 @@
     <t>location</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Location}
 </t>
   </si>
   <si>
@@ -515,7 +515,7 @@
     <t>requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_Requester}
 </t>
   </si>
   <si>
@@ -532,7 +532,7 @@
     <t>uncategorizedComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_UncategorizedComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationAdministration_UncategorizedComment}
 </t>
   </si>
   <si>
@@ -718,7 +718,7 @@
     <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -812,7 +812,7 @@
     <t>MedicationAdministration.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -909,7 +909,7 @@
     <t>MedicationAdministration.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|Procedure|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|Procedure)
 </t>
   </si>
   <si>
@@ -971,7 +971,7 @@
     <t>医薬品投与が取り消された理由を示すコードのセット</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-not-given-codes</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -995,7 +995,7 @@
     <t>薬剤の投与が予想される場所を記述するコード化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-admin-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-admin-category</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication usage"].value</t>
@@ -1004,7 +1004,7 @@
     <t>MedicationAdministration.medication[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication|1.3.0-dev)
+    <t xml:space="preserve">Reference(http://jpfhir.jp/fhir/core/StructureDefinition/JP_Medication)
 </t>
   </si>
   <si>
@@ -1037,7 +1037,7 @@
     <t>MedicationAdministration.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|4.0.1|Group|4.0.1)
+    <t xml:space="preserve">Reference(Patient|Group)
 </t>
   </si>
   <si>
@@ -1062,7 +1062,7 @@
     <t>MedicationAdministration.context</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter|4.0.1|EpisodeOfCare|4.0.1)
+    <t xml:space="preserve">Reference(Encounter|EpisodeOfCare)
 </t>
   </si>
   <si>
@@ -1087,7 +1087,7 @@
     <t>MedicationAdministration.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1197,7 +1197,7 @@
     <t>薬物管理を行った個人の役割を説明するコード</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/med-admin-perform-function</t>
   </si>
   <si>
     <t>Event.performer.function</t>
@@ -1209,7 +1209,7 @@
     <t>MedicationAdministration.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Patient|RelatedPerson|Device)
 </t>
   </si>
   <si>
@@ -1237,7 +1237,7 @@
     <t>薬剤投与が行われた理由を示すコードのセット。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/reason-medication-given-codes</t>
   </si>
   <si>
     <t>Event.reasonCode</t>
@@ -1252,7 +1252,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1)
+    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport)
 </t>
   </si>
   <si>
@@ -1280,7 +1280,7 @@
     <t>MedicationAdministration.request</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
+    <t xml:space="preserve">Reference(MedicationRequest)
 </t>
   </si>
   <si>
@@ -1305,7 +1305,7 @@
     <t>MedicationAdministration.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
+    <t xml:space="preserve">Reference(Device)
 </t>
   </si>
   <si>
@@ -1368,7 +1368,7 @@
     <t>dosageComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_DosageComment}
 </t>
   </si>
   <si>
@@ -1384,7 +1384,7 @@
     <t>device</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Device}
 </t>
   </si>
   <si>
@@ -1400,7 +1400,7 @@
     <t>line</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_Line}
 </t>
   </si>
   <si>
@@ -1416,7 +1416,7 @@
     <t>lineComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_LineComment}
 </t>
   </si>
   <si>
@@ -1432,7 +1432,7 @@
     <t>rateComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RateComment}
 </t>
   </si>
   <si>
@@ -1470,7 +1470,7 @@
     <t>ユースケースでBodySiteリソースの属性が必要な場合（たとえば、個別に識別して追跡するため）、標準の拡張機能[bodySite]（extension-bodysite.html）を使用する。要約コード、または場所の非常に正確な定義への参照、あるいはその両方である可能性がある。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationBodySiteJAMIExternal_VS</t>
   </si>
   <si>
     <t>.approachSiteCode</t>
@@ -1507,7 +1507,7 @@
     <t>siteComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_SiteComment}
 </t>
   </si>
   <si>
@@ -1578,7 +1578,7 @@
     <t>患者への、または患者への治療薬の投与経路または生理学的経路を指定するコード。たとえば、局所、静脈内など。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS|1.2.0</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationRouteHL70162_VS</t>
   </si>
   <si>
     <t>.routeCode</t>
@@ -1599,7 +1599,7 @@
     <t>routeComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_RouteComment}
 </t>
   </si>
   <si>
@@ -1630,7 +1630,7 @@
     <t>薬剤が投与される方法を記述する暗号化された概念。</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/administration-method-codes|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/administration-method-codes</t>
   </si>
   <si>
     <t>.methodCode</t>
@@ -1651,7 +1651,7 @@
     <t>methodComment</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment|1.3.0-dev}
+    <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/Extension/StructureDefinition/JP_MedicationDosage_MethodComment}
 </t>
   </si>
   <si>
@@ -1682,7 +1682,7 @@
     <t>他のコードシステムへの変換や代替のコードシステムを使ってエンコードしてもよい。</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIBasicUsage_VS</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit1.id</t>
@@ -1842,7 +1842,7 @@
     <t>投与⽅法に対応するJAMI 用法コード表基本用法2桁コードを識別するURI。２桁コードhttp://jami.jp/CodeSystem/MedicationUsage</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS|1.1.0a</t>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_MedicationMethodJAMIDetailUsage_VS</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.method.coding:unitDigit2.id</t>
@@ -1887,7 +1887,7 @@
     <t>MedicationAdministration.dosage.dose</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity|1.3.0-dev}
+    <t xml:space="preserve">Quantity {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationSimpleQuantity}
 </t>
   </si>
   <si>
@@ -1910,7 +1910,7 @@
   </si>
   <si>
     <t>Ratio
-Quantity {SimpleQuantity|4.0.1}</t>
+Quantity {SimpleQuantity}</t>
   </si>
   <si>
     <t>単位時間あたりの用量</t>
@@ -1942,7 +1942,7 @@
     <t>rateRatio</t>
   </si>
   <si>
-    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod|1.3.0-dev}
+    <t xml:space="preserve">Ratio {http://jpfhir.jp/fhir/core/StructureDefinition/JP_MedicationRatio_DosePerPeriod}
 </t>
   </si>
   <si>
@@ -1961,7 +1961,7 @@
     <t>rateQuantity</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1971,7 +1971,7 @@
     <t>MedicationAdministration.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance|4.0.1)
+    <t xml:space="preserve">Reference(Provenance)
 </t>
   </si>
   <si>
@@ -2301,7 +2301,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="103.5078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="95.515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2316,7 +2316,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="132.98828125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="64.84375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.3515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
